--- a/Project/ml-research/component_1_weather_tapping/data/raw/RubberSense_RawStyle_Synthetic_Dataset.xlsx
+++ b/Project/ml-research/component_1_weather_tapping/data/raw/RubberSense_RawStyle_Synthetic_Dataset.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V601"/>
+  <dimension ref="A1:W601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,6 +541,11 @@
           <t>estate_id</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>estate_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -625,6 +630,11 @@
           <t>EST-027</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>TBD_EST-027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -709,6 +719,11 @@
           <t>EST-018</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>TBD_EST-018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -793,6 +808,11 @@
           <t>EST-062</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TBD_EST-062</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -877,6 +897,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -961,6 +986,11 @@
           <t>EST-093</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>TBD_EST-093</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1045,6 +1075,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1129,6 +1164,11 @@
           <t>EST-075</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>TBD_EST-075</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1213,6 +1253,11 @@
           <t>EST-028</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1297,6 +1342,11 @@
           <t>EST-042</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>TBD_EST-042</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1381,6 +1431,11 @@
           <t>EST-098</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1465,6 +1520,11 @@
           <t>EST-027</t>
         </is>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>TBD_EST-027</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1549,6 +1609,11 @@
           <t>EST-102</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>TBD_EST-102</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1633,6 +1698,11 @@
           <t>EST-077</t>
         </is>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>TBD_EST-077</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1717,6 +1787,11 @@
           <t>EST-113</t>
         </is>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>TBD_EST-113</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1801,6 +1876,11 @@
           <t>EST-072</t>
         </is>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1885,6 +1965,11 @@
           <t>EST-036</t>
         </is>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>TBD_EST-036</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1969,6 +2054,11 @@
           <t>EST-017</t>
         </is>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>TBD_EST-017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2053,6 +2143,11 @@
           <t>EST-115</t>
         </is>
       </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>TBD_EST-115</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2137,6 +2232,11 @@
           <t>EST-092</t>
         </is>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>TBD_EST-092</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2221,6 +2321,11 @@
           <t>EST-038</t>
         </is>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>TBD_EST-038</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2305,6 +2410,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2389,6 +2499,11 @@
           <t>EST-091</t>
         </is>
       </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>TBD_EST-091</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2473,6 +2588,11 @@
           <t>EST-031</t>
         </is>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>TBD_EST-031</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2557,6 +2677,11 @@
           <t>EST-098</t>
         </is>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2641,6 +2766,11 @@
           <t>EST-035</t>
         </is>
       </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>TBD_EST-035</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2725,6 +2855,11 @@
           <t>EST-081</t>
         </is>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>TBD_EST-081</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2809,6 +2944,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2893,6 +3033,11 @@
           <t>EST-017</t>
         </is>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>TBD_EST-017</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2977,6 +3122,11 @@
           <t>EST-039</t>
         </is>
       </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>TBD_EST-039</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3061,6 +3211,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3145,6 +3300,11 @@
           <t>EST-016</t>
         </is>
       </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>TBD_EST-016</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3229,6 +3389,11 @@
           <t>EST-101</t>
         </is>
       </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3313,6 +3478,11 @@
           <t>EST-112</t>
         </is>
       </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>TBD_EST-112</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3397,6 +3567,11 @@
           <t>EST-012</t>
         </is>
       </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>TBD_EST-012</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3481,6 +3656,11 @@
           <t>EST-120</t>
         </is>
       </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>TBD_EST-120</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3563,6 +3743,11 @@
       <c r="V37" t="inlineStr">
         <is>
           <t>EST-096</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>TBD_EST-096</t>
         </is>
       </c>
     </row>
@@ -3647,6 +3832,11 @@
           <t>EST-048</t>
         </is>
       </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>TBD_EST-048</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3731,6 +3921,11 @@
           <t>EST-113</t>
         </is>
       </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>TBD_EST-113</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3815,6 +4010,11 @@
           <t>EST-072</t>
         </is>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3899,6 +4099,11 @@
           <t>EST-014</t>
         </is>
       </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>TBD_EST-014</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3983,6 +4188,11 @@
           <t>EST-013</t>
         </is>
       </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>TBD_EST-013</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4067,6 +4277,11 @@
           <t>EST-096</t>
         </is>
       </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>TBD_EST-096</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4151,6 +4366,11 @@
           <t>EST-107</t>
         </is>
       </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>TBD_EST-107</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4235,6 +4455,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4319,6 +4544,11 @@
           <t>EST-091</t>
         </is>
       </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>TBD_EST-091</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4403,6 +4633,11 @@
           <t>EST-107</t>
         </is>
       </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>TBD_EST-107</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4487,6 +4722,11 @@
           <t>EST-069</t>
         </is>
       </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>TBD_EST-069</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4571,6 +4811,11 @@
           <t>EST-003</t>
         </is>
       </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>TBD_EST-003</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4655,6 +4900,11 @@
           <t>EST-067</t>
         </is>
       </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>TBD_EST-067</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4739,6 +4989,11 @@
           <t>EST-035</t>
         </is>
       </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>TBD_EST-035</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4823,6 +5078,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4907,6 +5167,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4991,6 +5256,11 @@
           <t>EST-089</t>
         </is>
       </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>TBD_EST-089</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5075,6 +5345,11 @@
           <t>EST-003</t>
         </is>
       </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>TBD_EST-003</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5159,6 +5434,11 @@
           <t>EST-065</t>
         </is>
       </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>TBD_EST-065</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5243,6 +5523,11 @@
           <t>EST-119</t>
         </is>
       </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>TBD_EST-119</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5327,6 +5612,11 @@
           <t>EST-066</t>
         </is>
       </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>TBD_EST-066</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5411,6 +5701,11 @@
           <t>EST-081</t>
         </is>
       </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>TBD_EST-081</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5495,6 +5790,11 @@
           <t>EST-078</t>
         </is>
       </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>TBD_EST-078</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5579,6 +5879,11 @@
           <t>EST-035</t>
         </is>
       </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>TBD_EST-035</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5663,6 +5968,11 @@
           <t>EST-097</t>
         </is>
       </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>TBD_EST-097</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5747,6 +6057,11 @@
           <t>EST-063</t>
         </is>
       </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>TBD_EST-063</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5831,6 +6146,11 @@
           <t>EST-069</t>
         </is>
       </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>TBD_EST-069</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5915,6 +6235,11 @@
           <t>EST-093</t>
         </is>
       </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>TBD_EST-093</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5999,6 +6324,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6083,6 +6413,11 @@
           <t>EST-063</t>
         </is>
       </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>TBD_EST-063</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6167,6 +6502,11 @@
           <t>EST-040</t>
         </is>
       </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>TBD_EST-040</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6251,6 +6591,11 @@
           <t>EST-071</t>
         </is>
       </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>TBD_EST-071</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6335,6 +6680,11 @@
           <t>EST-065</t>
         </is>
       </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>TBD_EST-065</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6419,6 +6769,11 @@
           <t>EST-077</t>
         </is>
       </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>TBD_EST-077</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6503,6 +6858,11 @@
           <t>EST-084</t>
         </is>
       </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>TBD_EST-084</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6587,6 +6947,11 @@
           <t>EST-088</t>
         </is>
       </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>TBD_EST-088</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6671,6 +7036,11 @@
           <t>EST-115</t>
         </is>
       </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>TBD_EST-115</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6753,6 +7123,11 @@
       <c r="V75" t="inlineStr">
         <is>
           <t>EST-086</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>TBD_EST-086</t>
         </is>
       </c>
     </row>
@@ -6837,6 +7212,11 @@
           <t>EST-060</t>
         </is>
       </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>TBD_EST-060</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6921,6 +7301,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7005,6 +7390,11 @@
           <t>EST-018</t>
         </is>
       </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>TBD_EST-018</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7089,6 +7479,11 @@
           <t>EST-108</t>
         </is>
       </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>TBD_EST-108</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7173,6 +7568,11 @@
           <t>EST-068</t>
         </is>
       </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>TBD_EST-068</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7257,6 +7657,11 @@
           <t>EST-025</t>
         </is>
       </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>TBD_EST-025</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7341,6 +7746,11 @@
           <t>EST-086</t>
         </is>
       </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>TBD_EST-086</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7425,6 +7835,11 @@
           <t>EST-020</t>
         </is>
       </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>TBD_EST-020</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7509,6 +7924,11 @@
           <t>EST-033</t>
         </is>
       </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>TBD_EST-033</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7593,6 +8013,11 @@
           <t>EST-022</t>
         </is>
       </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>TBD_EST-022</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7677,6 +8102,11 @@
           <t>EST-056</t>
         </is>
       </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7761,6 +8191,11 @@
           <t>EST-077</t>
         </is>
       </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>TBD_EST-077</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7845,6 +8280,11 @@
           <t>EST-111</t>
         </is>
       </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>TBD_EST-111</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7929,6 +8369,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8013,6 +8458,11 @@
           <t>EST-056</t>
         </is>
       </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8097,6 +8547,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8181,6 +8636,11 @@
           <t>EST-006</t>
         </is>
       </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8265,6 +8725,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8349,6 +8814,11 @@
           <t>EST-082</t>
         </is>
       </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>TBD_EST-082</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8433,6 +8903,11 @@
           <t>EST-065</t>
         </is>
       </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>TBD_EST-065</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8517,6 +8992,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8601,6 +9081,11 @@
           <t>EST-050</t>
         </is>
       </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>TBD_EST-050</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8685,6 +9170,11 @@
           <t>EST-038</t>
         </is>
       </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>TBD_EST-038</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8769,6 +9259,11 @@
           <t>EST-057</t>
         </is>
       </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>TBD_EST-057</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8853,6 +9348,11 @@
           <t>EST-039</t>
         </is>
       </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>TBD_EST-039</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8937,6 +9437,11 @@
           <t>EST-083</t>
         </is>
       </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>TBD_EST-083</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9021,6 +9526,11 @@
           <t>EST-064</t>
         </is>
       </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>TBD_EST-064</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9105,6 +9615,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9189,6 +9704,11 @@
           <t>EST-119</t>
         </is>
       </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>TBD_EST-119</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9273,6 +9793,11 @@
           <t>EST-073</t>
         </is>
       </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>TBD_EST-073</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9357,6 +9882,11 @@
           <t>EST-084</t>
         </is>
       </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>TBD_EST-084</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9441,6 +9971,11 @@
           <t>EST-116</t>
         </is>
       </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>TBD_EST-116</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9525,6 +10060,11 @@
           <t>EST-050</t>
         </is>
       </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>TBD_EST-050</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9609,6 +10149,11 @@
           <t>EST-113</t>
         </is>
       </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>TBD_EST-113</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9693,6 +10238,11 @@
           <t>EST-053</t>
         </is>
       </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>TBD_EST-053</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9777,6 +10327,11 @@
           <t>EST-060</t>
         </is>
       </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>TBD_EST-060</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9861,6 +10416,11 @@
           <t>EST-039</t>
         </is>
       </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>TBD_EST-039</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9945,6 +10505,11 @@
           <t>EST-109</t>
         </is>
       </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10029,6 +10594,11 @@
           <t>EST-068</t>
         </is>
       </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>TBD_EST-068</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10113,6 +10683,11 @@
           <t>EST-017</t>
         </is>
       </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>TBD_EST-017</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10197,6 +10772,11 @@
           <t>EST-062</t>
         </is>
       </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>TBD_EST-062</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10281,6 +10861,11 @@
           <t>EST-120</t>
         </is>
       </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>TBD_EST-120</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10363,6 +10948,11 @@
       <c r="V118" t="inlineStr">
         <is>
           <t>EST-096</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>TBD_EST-096</t>
         </is>
       </c>
     </row>
@@ -10447,6 +11037,11 @@
           <t>EST-026</t>
         </is>
       </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>TBD_EST-026</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10531,6 +11126,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10615,6 +11215,11 @@
           <t>EST-047</t>
         </is>
       </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>TBD_EST-047</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10699,6 +11304,11 @@
           <t>EST-021</t>
         </is>
       </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>TBD_EST-021</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10783,6 +11393,11 @@
           <t>EST-076</t>
         </is>
       </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>TBD_EST-076</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10867,6 +11482,11 @@
           <t>EST-051</t>
         </is>
       </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>TBD_EST-051</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10951,6 +11571,11 @@
           <t>EST-052</t>
         </is>
       </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>TBD_EST-052</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11035,6 +11660,11 @@
           <t>EST-038</t>
         </is>
       </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>TBD_EST-038</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11117,6 +11747,11 @@
       <c r="V127" t="inlineStr">
         <is>
           <t>EST-028</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
         </is>
       </c>
     </row>
@@ -11201,6 +11836,11 @@
           <t>EST-068</t>
         </is>
       </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>TBD_EST-068</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11285,6 +11925,11 @@
           <t>EST-029</t>
         </is>
       </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>TBD_EST-029</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11369,6 +12014,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11451,6 +12101,11 @@
       <c r="V131" t="inlineStr">
         <is>
           <t>EST-106</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>TBD_EST-106</t>
         </is>
       </c>
     </row>
@@ -11535,6 +12190,11 @@
           <t>EST-095</t>
         </is>
       </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>TBD_EST-095</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11619,6 +12279,11 @@
           <t>EST-084</t>
         </is>
       </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>TBD_EST-084</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11703,6 +12368,11 @@
           <t>EST-026</t>
         </is>
       </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>TBD_EST-026</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11787,6 +12457,11 @@
           <t>EST-032</t>
         </is>
       </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>TBD_EST-032</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11871,6 +12546,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11955,6 +12635,11 @@
           <t>EST-074</t>
         </is>
       </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>TBD_EST-074</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12039,6 +12724,11 @@
           <t>EST-004</t>
         </is>
       </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>TBD_EST-004</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12123,6 +12813,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12207,6 +12902,11 @@
           <t>EST-017</t>
         </is>
       </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>TBD_EST-017</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12291,6 +12991,11 @@
           <t>EST-110</t>
         </is>
       </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>TBD_EST-110</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12375,6 +13080,11 @@
           <t>EST-101</t>
         </is>
       </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12459,6 +13169,11 @@
           <t>EST-014</t>
         </is>
       </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>TBD_EST-014</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12543,6 +13258,11 @@
           <t>EST-031</t>
         </is>
       </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>TBD_EST-031</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12627,6 +13347,11 @@
           <t>EST-008</t>
         </is>
       </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>TBD_EST-008</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12711,6 +13436,11 @@
           <t>EST-092</t>
         </is>
       </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>TBD_EST-092</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12795,6 +13525,11 @@
           <t>EST-093</t>
         </is>
       </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>TBD_EST-093</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12877,6 +13612,11 @@
       <c r="V148" t="inlineStr">
         <is>
           <t>EST-018</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>TBD_EST-018</t>
         </is>
       </c>
     </row>
@@ -12961,6 +13701,11 @@
           <t>EST-049</t>
         </is>
       </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>TBD_EST-049</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13045,6 +13790,11 @@
           <t>EST-051</t>
         </is>
       </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>TBD_EST-051</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13129,6 +13879,11 @@
           <t>EST-024</t>
         </is>
       </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>TBD_EST-024</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13213,6 +13968,11 @@
           <t>EST-046</t>
         </is>
       </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>TBD_EST-046</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13297,6 +14057,11 @@
           <t>EST-076</t>
         </is>
       </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>TBD_EST-076</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13379,6 +14144,11 @@
       <c r="V154" t="inlineStr">
         <is>
           <t>EST-056</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
         </is>
       </c>
     </row>
@@ -13463,6 +14233,11 @@
           <t>EST-079</t>
         </is>
       </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13547,6 +14322,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13631,6 +14411,11 @@
           <t>EST-097</t>
         </is>
       </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>TBD_EST-097</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13715,6 +14500,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13799,6 +14589,11 @@
           <t>EST-027</t>
         </is>
       </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>TBD_EST-027</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13883,6 +14678,11 @@
           <t>EST-078</t>
         </is>
       </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>TBD_EST-078</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13967,6 +14767,11 @@
           <t>EST-025</t>
         </is>
       </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>TBD_EST-025</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14051,6 +14856,11 @@
           <t>EST-061</t>
         </is>
       </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>TBD_EST-061</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14135,6 +14945,11 @@
           <t>EST-050</t>
         </is>
       </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>TBD_EST-050</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14219,6 +15034,11 @@
           <t>EST-004</t>
         </is>
       </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>TBD_EST-004</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14303,6 +15123,11 @@
           <t>EST-038</t>
         </is>
       </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>TBD_EST-038</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14387,6 +15212,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14471,6 +15301,11 @@
           <t>EST-032</t>
         </is>
       </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>TBD_EST-032</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14555,6 +15390,11 @@
           <t>EST-033</t>
         </is>
       </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>TBD_EST-033</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14639,6 +15479,11 @@
           <t>EST-018</t>
         </is>
       </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>TBD_EST-018</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14723,6 +15568,11 @@
           <t>EST-086</t>
         </is>
       </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>TBD_EST-086</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14807,6 +15657,11 @@
           <t>EST-083</t>
         </is>
       </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>TBD_EST-083</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14889,6 +15744,11 @@
       <c r="V172" t="inlineStr">
         <is>
           <t>EST-026</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>TBD_EST-026</t>
         </is>
       </c>
     </row>
@@ -14973,6 +15833,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15057,6 +15922,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15141,6 +16011,11 @@
           <t>EST-108</t>
         </is>
       </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>TBD_EST-108</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15225,6 +16100,11 @@
           <t>EST-099</t>
         </is>
       </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>TBD_EST-099</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15309,6 +16189,11 @@
           <t>EST-034</t>
         </is>
       </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>TBD_EST-034</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15393,6 +16278,11 @@
           <t>EST-098</t>
         </is>
       </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15477,6 +16367,11 @@
           <t>EST-079</t>
         </is>
       </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15561,6 +16456,11 @@
           <t>EST-047</t>
         </is>
       </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>TBD_EST-047</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15645,6 +16545,11 @@
           <t>EST-012</t>
         </is>
       </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>TBD_EST-012</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15729,6 +16634,11 @@
           <t>EST-101</t>
         </is>
       </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15813,6 +16723,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15897,6 +16812,11 @@
           <t>EST-037</t>
         </is>
       </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15981,6 +16901,11 @@
           <t>EST-062</t>
         </is>
       </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>TBD_EST-062</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -16065,6 +16990,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -16149,6 +17079,11 @@
           <t>EST-118</t>
         </is>
       </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>TBD_EST-118</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -16233,6 +17168,11 @@
           <t>EST-013</t>
         </is>
       </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>TBD_EST-013</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -16317,6 +17257,11 @@
           <t>EST-028</t>
         </is>
       </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -16401,6 +17346,11 @@
           <t>EST-016</t>
         </is>
       </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>TBD_EST-016</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -16485,6 +17435,11 @@
           <t>EST-102</t>
         </is>
       </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>TBD_EST-102</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -16567,6 +17522,11 @@
       <c r="V192" t="inlineStr">
         <is>
           <t>EST-048</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>TBD_EST-048</t>
         </is>
       </c>
     </row>
@@ -16651,6 +17611,11 @@
           <t>EST-043</t>
         </is>
       </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>TBD_EST-043</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -16735,6 +17700,11 @@
           <t>EST-042</t>
         </is>
       </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>TBD_EST-042</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16819,6 +17789,11 @@
           <t>EST-068</t>
         </is>
       </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>TBD_EST-068</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -16903,6 +17878,11 @@
           <t>EST-079</t>
         </is>
       </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -16987,6 +17967,11 @@
           <t>EST-046</t>
         </is>
       </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>TBD_EST-046</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -17071,6 +18056,11 @@
           <t>EST-072</t>
         </is>
       </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -17155,6 +18145,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -17239,6 +18234,11 @@
           <t>EST-029</t>
         </is>
       </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>TBD_EST-029</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -17323,6 +18323,11 @@
           <t>EST-095</t>
         </is>
       </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>TBD_EST-095</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -17407,6 +18412,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -17491,6 +18501,11 @@
           <t>EST-109</t>
         </is>
       </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -17575,6 +18590,11 @@
           <t>EST-031</t>
         </is>
       </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>TBD_EST-031</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -17659,6 +18679,11 @@
           <t>EST-067</t>
         </is>
       </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>TBD_EST-067</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -17741,6 +18766,11 @@
       <c r="V206" t="inlineStr">
         <is>
           <t>EST-087</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>TBD_EST-087</t>
         </is>
       </c>
     </row>
@@ -17825,6 +18855,11 @@
           <t>EST-088</t>
         </is>
       </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>TBD_EST-088</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -17907,6 +18942,11 @@
           <t>EST-029</t>
         </is>
       </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>TBD_EST-029</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -17991,6 +19031,11 @@
           <t>EST-110</t>
         </is>
       </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>TBD_EST-110</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -18075,6 +19120,11 @@
           <t>EST-098</t>
         </is>
       </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -18159,6 +19209,11 @@
           <t>EST-004</t>
         </is>
       </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>TBD_EST-004</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -18243,6 +19298,11 @@
           <t>EST-097</t>
         </is>
       </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>TBD_EST-097</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -18325,6 +19385,11 @@
       <c r="V213" t="inlineStr">
         <is>
           <t>EST-090</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
         </is>
       </c>
     </row>
@@ -18409,6 +19474,11 @@
           <t>EST-021</t>
         </is>
       </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>TBD_EST-021</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -18493,6 +19563,11 @@
           <t>EST-037</t>
         </is>
       </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -18577,6 +19652,11 @@
           <t>EST-010</t>
         </is>
       </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>TBD_EST-010</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -18661,6 +19741,11 @@
           <t>EST-093</t>
         </is>
       </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>TBD_EST-093</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -18745,6 +19830,11 @@
           <t>EST-037</t>
         </is>
       </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -18829,6 +19919,11 @@
           <t>EST-118</t>
         </is>
       </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>TBD_EST-118</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -18913,6 +20008,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -18997,6 +20097,11 @@
           <t>EST-053</t>
         </is>
       </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>TBD_EST-053</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -19081,6 +20186,11 @@
           <t>EST-051</t>
         </is>
       </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>TBD_EST-051</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -19165,6 +20275,11 @@
           <t>EST-018</t>
         </is>
       </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>TBD_EST-018</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -19249,6 +20364,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -19333,6 +20453,11 @@
           <t>EST-032</t>
         </is>
       </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>TBD_EST-032</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -19417,6 +20542,11 @@
           <t>EST-028</t>
         </is>
       </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -19501,6 +20631,11 @@
           <t>EST-056</t>
         </is>
       </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -19585,6 +20720,11 @@
           <t>EST-091</t>
         </is>
       </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>TBD_EST-091</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -19669,6 +20809,11 @@
           <t>EST-074</t>
         </is>
       </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>TBD_EST-074</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -19753,6 +20898,11 @@
           <t>EST-064</t>
         </is>
       </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>TBD_EST-064</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -19837,6 +20987,11 @@
           <t>EST-041</t>
         </is>
       </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>TBD_EST-041</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -19921,6 +21076,11 @@
           <t>EST-073</t>
         </is>
       </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>TBD_EST-073</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -20003,6 +21163,11 @@
       <c r="V233" t="inlineStr">
         <is>
           <t>EST-074</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>TBD_EST-074</t>
         </is>
       </c>
     </row>
@@ -20087,6 +21252,11 @@
           <t>EST-068</t>
         </is>
       </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>TBD_EST-068</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -20171,6 +21341,11 @@
           <t>EST-089</t>
         </is>
       </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>TBD_EST-089</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -20255,6 +21430,11 @@
           <t>EST-044</t>
         </is>
       </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>TBD_EST-044</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -20339,6 +21519,11 @@
           <t>EST-056</t>
         </is>
       </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -20423,6 +21608,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -20507,6 +21697,11 @@
           <t>EST-024</t>
         </is>
       </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>TBD_EST-024</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -20591,6 +21786,11 @@
           <t>EST-025</t>
         </is>
       </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>TBD_EST-025</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -20673,6 +21873,11 @@
       <c r="V241" t="inlineStr">
         <is>
           <t>EST-022</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>TBD_EST-022</t>
         </is>
       </c>
     </row>
@@ -20757,6 +21962,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -20841,6 +22051,11 @@
           <t>EST-022</t>
         </is>
       </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>TBD_EST-022</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -20925,6 +22140,11 @@
           <t>EST-073</t>
         </is>
       </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>TBD_EST-073</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -21007,6 +22227,11 @@
       <c r="V245" t="inlineStr">
         <is>
           <t>EST-041</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>TBD_EST-041</t>
         </is>
       </c>
     </row>
@@ -21091,6 +22316,11 @@
           <t>EST-004</t>
         </is>
       </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>TBD_EST-004</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -21175,6 +22405,11 @@
           <t>EST-034</t>
         </is>
       </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>TBD_EST-034</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -21259,6 +22494,11 @@
           <t>EST-118</t>
         </is>
       </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>TBD_EST-118</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -21343,6 +22583,11 @@
           <t>EST-055</t>
         </is>
       </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>TBD_EST-055</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -21427,6 +22672,11 @@
           <t>EST-100</t>
         </is>
       </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>TBD_EST-100</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -21511,6 +22761,11 @@
           <t>EST-051</t>
         </is>
       </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>TBD_EST-051</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -21595,6 +22850,11 @@
           <t>EST-052</t>
         </is>
       </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>TBD_EST-052</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -21679,6 +22939,11 @@
           <t>EST-081</t>
         </is>
       </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>TBD_EST-081</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -21763,6 +23028,11 @@
           <t>EST-067</t>
         </is>
       </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>TBD_EST-067</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -21847,6 +23117,11 @@
           <t>EST-079</t>
         </is>
       </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -21931,6 +23206,11 @@
           <t>EST-097</t>
         </is>
       </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>TBD_EST-097</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -22015,6 +23295,11 @@
           <t>EST-055</t>
         </is>
       </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>TBD_EST-055</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -22099,6 +23384,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -22183,6 +23473,11 @@
           <t>EST-081</t>
         </is>
       </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>TBD_EST-081</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -22267,6 +23562,11 @@
           <t>EST-001</t>
         </is>
       </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>TBD_EST-001</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -22351,6 +23651,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -22435,6 +23740,11 @@
           <t>EST-036</t>
         </is>
       </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>TBD_EST-036</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -22519,6 +23829,11 @@
           <t>EST-049</t>
         </is>
       </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>TBD_EST-049</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -22603,6 +23918,11 @@
           <t>EST-095</t>
         </is>
       </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>TBD_EST-095</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -22685,6 +24005,11 @@
       <c r="V265" t="inlineStr">
         <is>
           <t>EST-119</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>TBD_EST-119</t>
         </is>
       </c>
     </row>
@@ -22769,6 +24094,11 @@
           <t>EST-006</t>
         </is>
       </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -22853,6 +24183,11 @@
           <t>EST-064</t>
         </is>
       </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>TBD_EST-064</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -22937,6 +24272,11 @@
           <t>EST-057</t>
         </is>
       </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>TBD_EST-057</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -23021,6 +24361,11 @@
           <t>EST-006</t>
         </is>
       </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -23105,6 +24450,11 @@
           <t>EST-073</t>
         </is>
       </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>TBD_EST-073</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -23189,6 +24539,11 @@
           <t>EST-073</t>
         </is>
       </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>TBD_EST-073</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -23273,6 +24628,11 @@
           <t>EST-009</t>
         </is>
       </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>TBD_EST-009</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -23355,6 +24715,11 @@
       <c r="V273" t="inlineStr">
         <is>
           <t>EST-001</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>TBD_EST-001</t>
         </is>
       </c>
     </row>
@@ -23439,6 +24804,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -23523,6 +24893,11 @@
           <t>EST-072</t>
         </is>
       </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -23607,6 +24982,11 @@
           <t>EST-008</t>
         </is>
       </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>TBD_EST-008</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -23691,6 +25071,11 @@
           <t>EST-115</t>
         </is>
       </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>TBD_EST-115</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -23775,6 +25160,11 @@
           <t>EST-019</t>
         </is>
       </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>TBD_EST-019</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -23859,6 +25249,11 @@
           <t>EST-006</t>
         </is>
       </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -23943,6 +25338,11 @@
           <t>EST-061</t>
         </is>
       </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>TBD_EST-061</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -24027,6 +25427,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -24111,6 +25516,11 @@
           <t>EST-105</t>
         </is>
       </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>TBD_EST-105</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -24195,6 +25605,11 @@
           <t>EST-060</t>
         </is>
       </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>TBD_EST-060</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -24279,6 +25694,11 @@
           <t>EST-033</t>
         </is>
       </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>TBD_EST-033</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -24363,6 +25783,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -24447,6 +25872,11 @@
           <t>EST-097</t>
         </is>
       </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>TBD_EST-097</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -24531,6 +25961,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -24615,6 +26050,11 @@
           <t>EST-116</t>
         </is>
       </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>TBD_EST-116</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -24699,6 +26139,11 @@
           <t>EST-013</t>
         </is>
       </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>TBD_EST-013</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -24783,6 +26228,11 @@
           <t>EST-027</t>
         </is>
       </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>TBD_EST-027</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -24867,6 +26317,11 @@
           <t>EST-057</t>
         </is>
       </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>TBD_EST-057</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -24951,6 +26406,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -25035,6 +26495,11 @@
           <t>EST-065</t>
         </is>
       </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>TBD_EST-065</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -25119,6 +26584,11 @@
           <t>EST-003</t>
         </is>
       </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>TBD_EST-003</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -25203,6 +26673,11 @@
           <t>EST-105</t>
         </is>
       </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>TBD_EST-105</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -25287,6 +26762,11 @@
           <t>EST-048</t>
         </is>
       </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>TBD_EST-048</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -25371,6 +26851,11 @@
           <t>EST-066</t>
         </is>
       </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>TBD_EST-066</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -25455,6 +26940,11 @@
           <t>EST-072</t>
         </is>
       </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -25539,6 +27029,11 @@
           <t>EST-066</t>
         </is>
       </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>TBD_EST-066</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -25623,6 +27118,11 @@
           <t>EST-083</t>
         </is>
       </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>TBD_EST-083</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -25707,6 +27207,11 @@
           <t>EST-088</t>
         </is>
       </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>TBD_EST-088</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -25791,6 +27296,11 @@
           <t>EST-015</t>
         </is>
       </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>TBD_EST-015</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -25875,6 +27385,11 @@
           <t>EST-066</t>
         </is>
       </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>TBD_EST-066</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -25959,6 +27474,11 @@
           <t>EST-046</t>
         </is>
       </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>TBD_EST-046</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -26043,6 +27563,11 @@
           <t>EST-054</t>
         </is>
       </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>TBD_EST-054</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -26127,6 +27652,11 @@
           <t>EST-039</t>
         </is>
       </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>TBD_EST-039</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -26211,6 +27741,11 @@
           <t>EST-009</t>
         </is>
       </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>TBD_EST-009</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -26295,6 +27830,11 @@
           <t>EST-027</t>
         </is>
       </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>TBD_EST-027</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -26379,6 +27919,11 @@
           <t>EST-120</t>
         </is>
       </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>TBD_EST-120</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -26463,6 +28008,11 @@
           <t>EST-028</t>
         </is>
       </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -26547,6 +28097,11 @@
           <t>EST-012</t>
         </is>
       </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>TBD_EST-012</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -26631,6 +28186,11 @@
           <t>EST-049</t>
         </is>
       </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>TBD_EST-049</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -26715,6 +28275,11 @@
           <t>EST-117</t>
         </is>
       </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>TBD_EST-117</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -26799,6 +28364,11 @@
           <t>EST-084</t>
         </is>
       </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>TBD_EST-084</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -26883,6 +28453,11 @@
           <t>EST-064</t>
         </is>
       </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>TBD_EST-064</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -26967,6 +28542,11 @@
           <t>EST-010</t>
         </is>
       </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>TBD_EST-010</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -27051,6 +28631,11 @@
           <t>EST-091</t>
         </is>
       </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>TBD_EST-091</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -27135,6 +28720,11 @@
           <t>EST-086</t>
         </is>
       </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>TBD_EST-086</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -27219,6 +28809,11 @@
           <t>EST-082</t>
         </is>
       </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>TBD_EST-082</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -27303,6 +28898,11 @@
           <t>EST-007</t>
         </is>
       </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>TBD_EST-007</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -27387,6 +28987,11 @@
           <t>EST-065</t>
         </is>
       </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>TBD_EST-065</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -27471,6 +29076,11 @@
           <t>EST-078</t>
         </is>
       </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>TBD_EST-078</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -27555,6 +29165,11 @@
           <t>EST-104</t>
         </is>
       </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>TBD_EST-104</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -27639,6 +29254,11 @@
           <t>EST-004</t>
         </is>
       </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>TBD_EST-004</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -27723,6 +29343,11 @@
           <t>EST-101</t>
         </is>
       </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -27807,6 +29432,11 @@
           <t>EST-037</t>
         </is>
       </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -27891,6 +29521,11 @@
           <t>EST-038</t>
         </is>
       </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>TBD_EST-038</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -27975,6 +29610,11 @@
           <t>EST-076</t>
         </is>
       </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>TBD_EST-076</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -28059,6 +29699,11 @@
           <t>EST-012</t>
         </is>
       </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>TBD_EST-012</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -28143,6 +29788,11 @@
           <t>EST-083</t>
         </is>
       </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>TBD_EST-083</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -28227,6 +29877,11 @@
           <t>EST-004</t>
         </is>
       </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>TBD_EST-004</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -28311,6 +29966,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -28395,6 +30055,11 @@
           <t>EST-106</t>
         </is>
       </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>TBD_EST-106</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -28479,6 +30144,11 @@
           <t>EST-088</t>
         </is>
       </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>TBD_EST-088</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -28563,6 +30233,11 @@
           <t>EST-104</t>
         </is>
       </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>TBD_EST-104</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -28647,6 +30322,11 @@
           <t>EST-046</t>
         </is>
       </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>TBD_EST-046</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -28731,6 +30411,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -28815,6 +30500,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -28897,6 +30587,11 @@
       <c r="V339" t="inlineStr">
         <is>
           <t>EST-043</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>TBD_EST-043</t>
         </is>
       </c>
     </row>
@@ -28981,6 +30676,11 @@
           <t>EST-108</t>
         </is>
       </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>TBD_EST-108</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -29065,6 +30765,11 @@
           <t>EST-043</t>
         </is>
       </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>TBD_EST-043</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -29149,6 +30854,11 @@
           <t>EST-024</t>
         </is>
       </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>TBD_EST-024</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -29233,6 +30943,11 @@
           <t>EST-046</t>
         </is>
       </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>TBD_EST-046</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -29317,6 +31032,11 @@
           <t>EST-037</t>
         </is>
       </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -29401,6 +31121,11 @@
           <t>EST-086</t>
         </is>
       </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>TBD_EST-086</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -29485,6 +31210,11 @@
           <t>EST-026</t>
         </is>
       </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>TBD_EST-026</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -29569,6 +31299,11 @@
           <t>EST-043</t>
         </is>
       </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>TBD_EST-043</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -29653,6 +31388,11 @@
           <t>EST-004</t>
         </is>
       </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>TBD_EST-004</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -29737,6 +31477,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -29821,6 +31566,11 @@
           <t>EST-065</t>
         </is>
       </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>TBD_EST-065</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -29905,6 +31655,11 @@
           <t>EST-048</t>
         </is>
       </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>TBD_EST-048</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -29987,6 +31742,11 @@
       <c r="V352" t="inlineStr">
         <is>
           <t>EST-062</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>TBD_EST-062</t>
         </is>
       </c>
     </row>
@@ -30071,6 +31831,11 @@
           <t>EST-104</t>
         </is>
       </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>TBD_EST-104</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -30155,6 +31920,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -30239,6 +32009,11 @@
           <t>EST-095</t>
         </is>
       </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>TBD_EST-095</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -30323,6 +32098,11 @@
           <t>EST-115</t>
         </is>
       </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>TBD_EST-115</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -30407,6 +32187,11 @@
           <t>EST-113</t>
         </is>
       </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>TBD_EST-113</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -30491,6 +32276,11 @@
           <t>EST-002</t>
         </is>
       </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>TBD_EST-002</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -30575,6 +32365,11 @@
           <t>EST-066</t>
         </is>
       </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>TBD_EST-066</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -30659,6 +32454,11 @@
           <t>EST-031</t>
         </is>
       </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>TBD_EST-031</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -30743,6 +32543,11 @@
           <t>EST-001</t>
         </is>
       </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>TBD_EST-001</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -30827,6 +32632,11 @@
           <t>EST-116</t>
         </is>
       </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>TBD_EST-116</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -30911,6 +32721,11 @@
           <t>EST-043</t>
         </is>
       </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>TBD_EST-043</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -30995,6 +32810,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -31079,6 +32899,11 @@
           <t>EST-061</t>
         </is>
       </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>TBD_EST-061</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -31163,6 +32988,11 @@
           <t>EST-086</t>
         </is>
       </c>
+      <c r="W366" t="inlineStr">
+        <is>
+          <t>TBD_EST-086</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -31247,6 +33077,11 @@
           <t>EST-040</t>
         </is>
       </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>TBD_EST-040</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -31331,6 +33166,11 @@
           <t>EST-089</t>
         </is>
       </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>TBD_EST-089</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -31415,6 +33255,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -31499,6 +33344,11 @@
           <t>EST-061</t>
         </is>
       </c>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>TBD_EST-061</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -31583,6 +33433,11 @@
           <t>EST-062</t>
         </is>
       </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>TBD_EST-062</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -31667,6 +33522,11 @@
           <t>EST-119</t>
         </is>
       </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>TBD_EST-119</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -31751,6 +33611,11 @@
           <t>EST-010</t>
         </is>
       </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>TBD_EST-010</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -31835,6 +33700,11 @@
           <t>EST-050</t>
         </is>
       </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>TBD_EST-050</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -31919,6 +33789,11 @@
           <t>EST-076</t>
         </is>
       </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>TBD_EST-076</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -32003,6 +33878,11 @@
           <t>EST-011</t>
         </is>
       </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>TBD_EST-011</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -32087,6 +33967,11 @@
           <t>EST-026</t>
         </is>
       </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>TBD_EST-026</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -32171,6 +34056,11 @@
           <t>EST-118</t>
         </is>
       </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>TBD_EST-118</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -32255,6 +34145,11 @@
           <t>EST-016</t>
         </is>
       </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>TBD_EST-016</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -32339,6 +34234,11 @@
           <t>EST-093</t>
         </is>
       </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>TBD_EST-093</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -32423,6 +34323,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -32507,6 +34412,11 @@
           <t>EST-056</t>
         </is>
       </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -32591,6 +34501,11 @@
           <t>EST-109</t>
         </is>
       </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -32675,6 +34590,11 @@
           <t>EST-065</t>
         </is>
       </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>TBD_EST-065</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -32759,6 +34679,11 @@
           <t>EST-116</t>
         </is>
       </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>TBD_EST-116</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -32843,6 +34768,11 @@
           <t>EST-045</t>
         </is>
       </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>TBD_EST-045</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -32927,6 +34857,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -33011,6 +34946,11 @@
           <t>EST-107</t>
         </is>
       </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>TBD_EST-107</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -33095,6 +35035,11 @@
           <t>EST-097</t>
         </is>
       </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>TBD_EST-097</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -33179,6 +35124,11 @@
           <t>EST-014</t>
         </is>
       </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>TBD_EST-014</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -33263,6 +35213,11 @@
           <t>EST-006</t>
         </is>
       </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -33347,6 +35302,11 @@
           <t>EST-101</t>
         </is>
       </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -33431,6 +35391,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -33515,6 +35480,11 @@
           <t>EST-117</t>
         </is>
       </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>TBD_EST-117</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -33599,6 +35569,11 @@
           <t>EST-080</t>
         </is>
       </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>TBD_EST-080</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -33683,6 +35658,11 @@
           <t>EST-105</t>
         </is>
       </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>TBD_EST-105</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -33767,6 +35747,11 @@
           <t>EST-061</t>
         </is>
       </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>TBD_EST-061</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -33851,6 +35836,11 @@
           <t>EST-101</t>
         </is>
       </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -33933,6 +35923,11 @@
       <c r="V399" t="inlineStr">
         <is>
           <t>EST-010</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>TBD_EST-010</t>
         </is>
       </c>
     </row>
@@ -34017,6 +36012,11 @@
           <t>EST-098</t>
         </is>
       </c>
+      <c r="W400" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -34101,6 +36101,11 @@
           <t>EST-087</t>
         </is>
       </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>TBD_EST-087</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -34185,6 +36190,11 @@
           <t>EST-045</t>
         </is>
       </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>TBD_EST-045</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -34269,6 +36279,11 @@
           <t>EST-072</t>
         </is>
       </c>
+      <c r="W403" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -34353,6 +36368,11 @@
           <t>EST-020</t>
         </is>
       </c>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>TBD_EST-020</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -34437,6 +36457,11 @@
           <t>EST-031</t>
         </is>
       </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>TBD_EST-031</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -34521,6 +36546,11 @@
           <t>EST-079</t>
         </is>
       </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -34605,6 +36635,11 @@
           <t>EST-114</t>
         </is>
       </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>TBD_EST-114</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -34689,6 +36724,11 @@
           <t>EST-117</t>
         </is>
       </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>TBD_EST-117</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -34773,6 +36813,11 @@
           <t>EST-063</t>
         </is>
       </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>TBD_EST-063</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -34857,6 +36902,11 @@
           <t>EST-098</t>
         </is>
       </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -34941,6 +36991,11 @@
           <t>EST-107</t>
         </is>
       </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>TBD_EST-107</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -35025,6 +37080,11 @@
           <t>EST-067</t>
         </is>
       </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>TBD_EST-067</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -35109,6 +37169,11 @@
           <t>EST-082</t>
         </is>
       </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>TBD_EST-082</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -35193,6 +37258,11 @@
           <t>EST-106</t>
         </is>
       </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>TBD_EST-106</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -35277,6 +37347,11 @@
           <t>EST-073</t>
         </is>
       </c>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>TBD_EST-073</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -35361,6 +37436,11 @@
           <t>EST-100</t>
         </is>
       </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>TBD_EST-100</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -35445,6 +37525,11 @@
           <t>EST-010</t>
         </is>
       </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>TBD_EST-010</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -35529,6 +37614,11 @@
           <t>EST-005</t>
         </is>
       </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>TBD_EST-005</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -35613,6 +37703,11 @@
           <t>EST-032</t>
         </is>
       </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>TBD_EST-032</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -35697,6 +37792,11 @@
           <t>EST-006</t>
         </is>
       </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -35781,6 +37881,11 @@
           <t>EST-075</t>
         </is>
       </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>TBD_EST-075</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -35865,6 +37970,11 @@
           <t>EST-096</t>
         </is>
       </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>TBD_EST-096</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -35949,6 +38059,11 @@
           <t>EST-051</t>
         </is>
       </c>
+      <c r="W423" t="inlineStr">
+        <is>
+          <t>TBD_EST-051</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -36033,6 +38148,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -36117,6 +38237,11 @@
           <t>EST-035</t>
         </is>
       </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>TBD_EST-035</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -36201,6 +38326,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -36285,6 +38415,11 @@
           <t>EST-116</t>
         </is>
       </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>TBD_EST-116</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -36369,6 +38504,11 @@
           <t>EST-076</t>
         </is>
       </c>
+      <c r="W428" t="inlineStr">
+        <is>
+          <t>TBD_EST-076</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -36453,6 +38593,11 @@
           <t>EST-095</t>
         </is>
       </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>TBD_EST-095</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -36537,6 +38682,11 @@
           <t>EST-031</t>
         </is>
       </c>
+      <c r="W430" t="inlineStr">
+        <is>
+          <t>TBD_EST-031</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -36621,6 +38771,11 @@
           <t>EST-056</t>
         </is>
       </c>
+      <c r="W431" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -36705,6 +38860,11 @@
           <t>EST-039</t>
         </is>
       </c>
+      <c r="W432" t="inlineStr">
+        <is>
+          <t>TBD_EST-039</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -36789,6 +38949,11 @@
           <t>EST-056</t>
         </is>
       </c>
+      <c r="W433" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -36873,6 +39038,11 @@
           <t>EST-034</t>
         </is>
       </c>
+      <c r="W434" t="inlineStr">
+        <is>
+          <t>TBD_EST-034</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -36957,6 +39127,11 @@
           <t>EST-078</t>
         </is>
       </c>
+      <c r="W435" t="inlineStr">
+        <is>
+          <t>TBD_EST-078</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -37041,6 +39216,11 @@
           <t>EST-002</t>
         </is>
       </c>
+      <c r="W436" t="inlineStr">
+        <is>
+          <t>TBD_EST-002</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -37125,6 +39305,11 @@
           <t>EST-097</t>
         </is>
       </c>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>TBD_EST-097</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -37209,6 +39394,11 @@
           <t>EST-111</t>
         </is>
       </c>
+      <c r="W438" t="inlineStr">
+        <is>
+          <t>TBD_EST-111</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -37293,6 +39483,11 @@
           <t>EST-091</t>
         </is>
       </c>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>TBD_EST-091</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -37377,6 +39572,11 @@
           <t>EST-007</t>
         </is>
       </c>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>TBD_EST-007</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -37461,6 +39661,11 @@
           <t>EST-061</t>
         </is>
       </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>TBD_EST-061</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -37545,6 +39750,11 @@
           <t>EST-100</t>
         </is>
       </c>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>TBD_EST-100</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -37629,6 +39839,11 @@
           <t>EST-008</t>
         </is>
       </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>TBD_EST-008</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -37713,6 +39928,11 @@
           <t>EST-014</t>
         </is>
       </c>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>TBD_EST-014</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -37797,6 +40017,11 @@
           <t>EST-062</t>
         </is>
       </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>TBD_EST-062</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -37881,6 +40106,11 @@
           <t>EST-062</t>
         </is>
       </c>
+      <c r="W446" t="inlineStr">
+        <is>
+          <t>TBD_EST-062</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -37965,6 +40195,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -38049,6 +40284,11 @@
           <t>EST-072</t>
         </is>
       </c>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -38133,6 +40373,11 @@
           <t>EST-038</t>
         </is>
       </c>
+      <c r="W449" t="inlineStr">
+        <is>
+          <t>TBD_EST-038</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -38217,6 +40462,11 @@
           <t>EST-028</t>
         </is>
       </c>
+      <c r="W450" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -38301,6 +40551,11 @@
           <t>EST-047</t>
         </is>
       </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>TBD_EST-047</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -38385,6 +40640,11 @@
           <t>EST-011</t>
         </is>
       </c>
+      <c r="W452" t="inlineStr">
+        <is>
+          <t>TBD_EST-011</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -38469,6 +40729,11 @@
           <t>EST-024</t>
         </is>
       </c>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>TBD_EST-024</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -38553,6 +40818,11 @@
           <t>EST-089</t>
         </is>
       </c>
+      <c r="W454" t="inlineStr">
+        <is>
+          <t>TBD_EST-089</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -38635,6 +40905,11 @@
       <c r="V455" t="inlineStr">
         <is>
           <t>EST-017</t>
+        </is>
+      </c>
+      <c r="W455" t="inlineStr">
+        <is>
+          <t>TBD_EST-017</t>
         </is>
       </c>
     </row>
@@ -38719,6 +40994,11 @@
           <t>EST-015</t>
         </is>
       </c>
+      <c r="W456" t="inlineStr">
+        <is>
+          <t>TBD_EST-015</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -38803,6 +41083,11 @@
           <t>EST-036</t>
         </is>
       </c>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>TBD_EST-036</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -38885,6 +41170,11 @@
       <c r="V458" t="inlineStr">
         <is>
           <t>EST-039</t>
+        </is>
+      </c>
+      <c r="W458" t="inlineStr">
+        <is>
+          <t>TBD_EST-039</t>
         </is>
       </c>
     </row>
@@ -38969,6 +41259,11 @@
           <t>EST-069</t>
         </is>
       </c>
+      <c r="W459" t="inlineStr">
+        <is>
+          <t>TBD_EST-069</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -39053,6 +41348,11 @@
           <t>EST-025</t>
         </is>
       </c>
+      <c r="W460" t="inlineStr">
+        <is>
+          <t>TBD_EST-025</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -39137,6 +41437,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W461" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -39221,6 +41526,11 @@
           <t>EST-011</t>
         </is>
       </c>
+      <c r="W462" t="inlineStr">
+        <is>
+          <t>TBD_EST-011</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -39305,6 +41615,11 @@
           <t>EST-008</t>
         </is>
       </c>
+      <c r="W463" t="inlineStr">
+        <is>
+          <t>TBD_EST-008</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -39389,6 +41704,11 @@
           <t>EST-092</t>
         </is>
       </c>
+      <c r="W464" t="inlineStr">
+        <is>
+          <t>TBD_EST-092</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -39473,6 +41793,11 @@
           <t>EST-088</t>
         </is>
       </c>
+      <c r="W465" t="inlineStr">
+        <is>
+          <t>TBD_EST-088</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -39557,6 +41882,11 @@
           <t>EST-023</t>
         </is>
       </c>
+      <c r="W466" t="inlineStr">
+        <is>
+          <t>TBD_EST-023</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -39641,6 +41971,11 @@
           <t>EST-035</t>
         </is>
       </c>
+      <c r="W467" t="inlineStr">
+        <is>
+          <t>TBD_EST-035</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -39725,6 +42060,11 @@
           <t>EST-091</t>
         </is>
       </c>
+      <c r="W468" t="inlineStr">
+        <is>
+          <t>TBD_EST-091</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -39809,6 +42149,11 @@
           <t>EST-081</t>
         </is>
       </c>
+      <c r="W469" t="inlineStr">
+        <is>
+          <t>TBD_EST-081</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -39893,6 +42238,11 @@
           <t>EST-089</t>
         </is>
       </c>
+      <c r="W470" t="inlineStr">
+        <is>
+          <t>TBD_EST-089</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -39977,6 +42327,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W471" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -40061,6 +42416,11 @@
           <t>EST-111</t>
         </is>
       </c>
+      <c r="W472" t="inlineStr">
+        <is>
+          <t>TBD_EST-111</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -40145,6 +42505,11 @@
           <t>EST-027</t>
         </is>
       </c>
+      <c r="W473" t="inlineStr">
+        <is>
+          <t>TBD_EST-027</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -40229,6 +42594,11 @@
           <t>EST-108</t>
         </is>
       </c>
+      <c r="W474" t="inlineStr">
+        <is>
+          <t>TBD_EST-108</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -40313,6 +42683,11 @@
           <t>EST-074</t>
         </is>
       </c>
+      <c r="W475" t="inlineStr">
+        <is>
+          <t>TBD_EST-074</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -40397,6 +42772,11 @@
           <t>EST-033</t>
         </is>
       </c>
+      <c r="W476" t="inlineStr">
+        <is>
+          <t>TBD_EST-033</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -40481,6 +42861,11 @@
           <t>EST-079</t>
         </is>
       </c>
+      <c r="W477" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -40565,6 +42950,11 @@
           <t>EST-034</t>
         </is>
       </c>
+      <c r="W478" t="inlineStr">
+        <is>
+          <t>TBD_EST-034</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -40649,6 +43039,11 @@
           <t>EST-058</t>
         </is>
       </c>
+      <c r="W479" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -40733,6 +43128,11 @@
           <t>EST-084</t>
         </is>
       </c>
+      <c r="W480" t="inlineStr">
+        <is>
+          <t>TBD_EST-084</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -40817,6 +43217,11 @@
           <t>EST-051</t>
         </is>
       </c>
+      <c r="W481" t="inlineStr">
+        <is>
+          <t>TBD_EST-051</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -40901,6 +43306,11 @@
           <t>EST-078</t>
         </is>
       </c>
+      <c r="W482" t="inlineStr">
+        <is>
+          <t>TBD_EST-078</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -40985,6 +43395,11 @@
           <t>EST-099</t>
         </is>
       </c>
+      <c r="W483" t="inlineStr">
+        <is>
+          <t>TBD_EST-099</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -41069,6 +43484,11 @@
           <t>EST-015</t>
         </is>
       </c>
+      <c r="W484" t="inlineStr">
+        <is>
+          <t>TBD_EST-015</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -41153,6 +43573,11 @@
           <t>EST-008</t>
         </is>
       </c>
+      <c r="W485" t="inlineStr">
+        <is>
+          <t>TBD_EST-008</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -41237,6 +43662,11 @@
           <t>EST-098</t>
         </is>
       </c>
+      <c r="W486" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -41321,6 +43751,11 @@
           <t>EST-109</t>
         </is>
       </c>
+      <c r="W487" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -41405,6 +43840,11 @@
           <t>EST-083</t>
         </is>
       </c>
+      <c r="W488" t="inlineStr">
+        <is>
+          <t>TBD_EST-083</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -41489,6 +43929,11 @@
           <t>EST-007</t>
         </is>
       </c>
+      <c r="W489" t="inlineStr">
+        <is>
+          <t>TBD_EST-007</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -41573,6 +44018,11 @@
           <t>EST-001</t>
         </is>
       </c>
+      <c r="W490" t="inlineStr">
+        <is>
+          <t>TBD_EST-001</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -41657,6 +44107,11 @@
           <t>EST-053</t>
         </is>
       </c>
+      <c r="W491" t="inlineStr">
+        <is>
+          <t>TBD_EST-053</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -41741,6 +44196,11 @@
           <t>EST-084</t>
         </is>
       </c>
+      <c r="W492" t="inlineStr">
+        <is>
+          <t>TBD_EST-084</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -41825,6 +44285,11 @@
           <t>EST-076</t>
         </is>
       </c>
+      <c r="W493" t="inlineStr">
+        <is>
+          <t>TBD_EST-076</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -41909,6 +44374,11 @@
           <t>EST-088</t>
         </is>
       </c>
+      <c r="W494" t="inlineStr">
+        <is>
+          <t>TBD_EST-088</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -41993,6 +44463,11 @@
           <t>EST-020</t>
         </is>
       </c>
+      <c r="W495" t="inlineStr">
+        <is>
+          <t>TBD_EST-020</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -42077,6 +44552,11 @@
           <t>EST-053</t>
         </is>
       </c>
+      <c r="W496" t="inlineStr">
+        <is>
+          <t>TBD_EST-053</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -42161,6 +44641,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W497" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -42245,6 +44730,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W498" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -42329,6 +44819,11 @@
           <t>EST-032</t>
         </is>
       </c>
+      <c r="W499" t="inlineStr">
+        <is>
+          <t>TBD_EST-032</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -42413,6 +44908,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W500" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -42497,6 +44997,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W501" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -42581,6 +45086,11 @@
           <t>EST-057</t>
         </is>
       </c>
+      <c r="W502" t="inlineStr">
+        <is>
+          <t>TBD_EST-057</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -42665,6 +45175,11 @@
           <t>EST-117</t>
         </is>
       </c>
+      <c r="W503" t="inlineStr">
+        <is>
+          <t>TBD_EST-117</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -42749,6 +45264,11 @@
           <t>EST-021</t>
         </is>
       </c>
+      <c r="W504" t="inlineStr">
+        <is>
+          <t>TBD_EST-021</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -42833,6 +45353,11 @@
           <t>EST-034</t>
         </is>
       </c>
+      <c r="W505" t="inlineStr">
+        <is>
+          <t>TBD_EST-034</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -42917,6 +45442,11 @@
           <t>EST-019</t>
         </is>
       </c>
+      <c r="W506" t="inlineStr">
+        <is>
+          <t>TBD_EST-019</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -43001,6 +45531,11 @@
           <t>EST-035</t>
         </is>
       </c>
+      <c r="W507" t="inlineStr">
+        <is>
+          <t>TBD_EST-035</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -43085,6 +45620,11 @@
           <t>EST-015</t>
         </is>
       </c>
+      <c r="W508" t="inlineStr">
+        <is>
+          <t>TBD_EST-015</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -43169,6 +45709,11 @@
           <t>EST-096</t>
         </is>
       </c>
+      <c r="W509" t="inlineStr">
+        <is>
+          <t>TBD_EST-096</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -43253,6 +45798,11 @@
           <t>EST-082</t>
         </is>
       </c>
+      <c r="W510" t="inlineStr">
+        <is>
+          <t>TBD_EST-082</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -43337,6 +45887,11 @@
           <t>EST-005</t>
         </is>
       </c>
+      <c r="W511" t="inlineStr">
+        <is>
+          <t>TBD_EST-005</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -43421,6 +45976,11 @@
           <t>EST-073</t>
         </is>
       </c>
+      <c r="W512" t="inlineStr">
+        <is>
+          <t>TBD_EST-073</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -43505,6 +46065,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W513" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -43589,6 +46154,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W514" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -43673,6 +46243,11 @@
           <t>EST-005</t>
         </is>
       </c>
+      <c r="W515" t="inlineStr">
+        <is>
+          <t>TBD_EST-005</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -43757,6 +46332,11 @@
           <t>EST-104</t>
         </is>
       </c>
+      <c r="W516" t="inlineStr">
+        <is>
+          <t>TBD_EST-104</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -43841,6 +46421,11 @@
           <t>EST-024</t>
         </is>
       </c>
+      <c r="W517" t="inlineStr">
+        <is>
+          <t>TBD_EST-024</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -43925,6 +46510,11 @@
           <t>EST-024</t>
         </is>
       </c>
+      <c r="W518" t="inlineStr">
+        <is>
+          <t>TBD_EST-024</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -44009,6 +46599,11 @@
           <t>EST-038</t>
         </is>
       </c>
+      <c r="W519" t="inlineStr">
+        <is>
+          <t>TBD_EST-038</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -44093,6 +46688,11 @@
           <t>EST-043</t>
         </is>
       </c>
+      <c r="W520" t="inlineStr">
+        <is>
+          <t>TBD_EST-043</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -44177,6 +46777,11 @@
           <t>EST-070</t>
         </is>
       </c>
+      <c r="W521" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -44261,6 +46866,11 @@
           <t>EST-013</t>
         </is>
       </c>
+      <c r="W522" t="inlineStr">
+        <is>
+          <t>TBD_EST-013</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -44345,6 +46955,11 @@
           <t>EST-109</t>
         </is>
       </c>
+      <c r="W523" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -44429,6 +47044,11 @@
           <t>EST-040</t>
         </is>
       </c>
+      <c r="W524" t="inlineStr">
+        <is>
+          <t>TBD_EST-040</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -44513,6 +47133,11 @@
           <t>EST-015</t>
         </is>
       </c>
+      <c r="W525" t="inlineStr">
+        <is>
+          <t>TBD_EST-015</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -44597,6 +47222,11 @@
           <t>EST-036</t>
         </is>
       </c>
+      <c r="W526" t="inlineStr">
+        <is>
+          <t>TBD_EST-036</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -44681,6 +47311,11 @@
           <t>EST-096</t>
         </is>
       </c>
+      <c r="W527" t="inlineStr">
+        <is>
+          <t>TBD_EST-096</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -44763,6 +47398,11 @@
       <c r="V528" t="inlineStr">
         <is>
           <t>EST-037</t>
+        </is>
+      </c>
+      <c r="W528" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
         </is>
       </c>
     </row>
@@ -44847,6 +47487,11 @@
           <t>EST-113</t>
         </is>
       </c>
+      <c r="W529" t="inlineStr">
+        <is>
+          <t>TBD_EST-113</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -44931,6 +47576,11 @@
           <t>EST-030</t>
         </is>
       </c>
+      <c r="W530" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -45013,6 +47663,11 @@
       <c r="V531" t="inlineStr">
         <is>
           <t>EST-109</t>
+        </is>
+      </c>
+      <c r="W531" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
         </is>
       </c>
     </row>
@@ -45097,6 +47752,11 @@
           <t>EST-067</t>
         </is>
       </c>
+      <c r="W532" t="inlineStr">
+        <is>
+          <t>TBD_EST-067</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -45181,6 +47841,11 @@
           <t>EST-028</t>
         </is>
       </c>
+      <c r="W533" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -45265,6 +47930,11 @@
           <t>EST-013</t>
         </is>
       </c>
+      <c r="W534" t="inlineStr">
+        <is>
+          <t>TBD_EST-013</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -45349,6 +48019,11 @@
           <t>EST-019</t>
         </is>
       </c>
+      <c r="W535" t="inlineStr">
+        <is>
+          <t>TBD_EST-019</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -45433,6 +48108,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W536" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -45517,6 +48197,11 @@
           <t>EST-087</t>
         </is>
       </c>
+      <c r="W537" t="inlineStr">
+        <is>
+          <t>TBD_EST-087</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -45601,6 +48286,11 @@
           <t>EST-017</t>
         </is>
       </c>
+      <c r="W538" t="inlineStr">
+        <is>
+          <t>TBD_EST-017</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -45685,6 +48375,11 @@
           <t>EST-028</t>
         </is>
       </c>
+      <c r="W539" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -45769,6 +48464,11 @@
           <t>EST-034</t>
         </is>
       </c>
+      <c r="W540" t="inlineStr">
+        <is>
+          <t>TBD_EST-034</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -45853,6 +48553,11 @@
           <t>EST-072</t>
         </is>
       </c>
+      <c r="W541" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -45937,6 +48642,11 @@
           <t>EST-012</t>
         </is>
       </c>
+      <c r="W542" t="inlineStr">
+        <is>
+          <t>TBD_EST-012</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -46019,6 +48729,11 @@
       <c r="V543" t="inlineStr">
         <is>
           <t>EST-119</t>
+        </is>
+      </c>
+      <c r="W543" t="inlineStr">
+        <is>
+          <t>TBD_EST-119</t>
         </is>
       </c>
     </row>
@@ -46103,6 +48818,11 @@
           <t>EST-109</t>
         </is>
       </c>
+      <c r="W544" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -46187,6 +48907,11 @@
           <t>EST-008</t>
         </is>
       </c>
+      <c r="W545" t="inlineStr">
+        <is>
+          <t>TBD_EST-008</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -46271,6 +48996,11 @@
           <t>EST-021</t>
         </is>
       </c>
+      <c r="W546" t="inlineStr">
+        <is>
+          <t>TBD_EST-021</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -46355,6 +49085,11 @@
           <t>EST-059</t>
         </is>
       </c>
+      <c r="W547" t="inlineStr">
+        <is>
+          <t>TBD_EST-059</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -46439,6 +49174,11 @@
           <t>EST-075</t>
         </is>
       </c>
+      <c r="W548" t="inlineStr">
+        <is>
+          <t>TBD_EST-075</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -46523,6 +49263,11 @@
           <t>EST-119</t>
         </is>
       </c>
+      <c r="W549" t="inlineStr">
+        <is>
+          <t>TBD_EST-119</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -46607,6 +49352,11 @@
           <t>EST-090</t>
         </is>
       </c>
+      <c r="W550" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -46691,6 +49441,11 @@
           <t>EST-083</t>
         </is>
       </c>
+      <c r="W551" t="inlineStr">
+        <is>
+          <t>TBD_EST-083</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -46775,6 +49530,11 @@
           <t>EST-032</t>
         </is>
       </c>
+      <c r="W552" t="inlineStr">
+        <is>
+          <t>TBD_EST-032</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -46859,6 +49619,11 @@
           <t>EST-079</t>
         </is>
       </c>
+      <c r="W553" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -46943,6 +49708,11 @@
           <t>EST-012</t>
         </is>
       </c>
+      <c r="W554" t="inlineStr">
+        <is>
+          <t>TBD_EST-012</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -47027,6 +49797,11 @@
           <t>EST-104</t>
         </is>
       </c>
+      <c r="W555" t="inlineStr">
+        <is>
+          <t>TBD_EST-104</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -47111,6 +49886,11 @@
           <t>EST-066</t>
         </is>
       </c>
+      <c r="W556" t="inlineStr">
+        <is>
+          <t>TBD_EST-066</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -47195,6 +49975,11 @@
           <t>EST-014</t>
         </is>
       </c>
+      <c r="W557" t="inlineStr">
+        <is>
+          <t>TBD_EST-014</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -47277,6 +50062,11 @@
       <c r="V558" t="inlineStr">
         <is>
           <t>EST-039</t>
+        </is>
+      </c>
+      <c r="W558" t="inlineStr">
+        <is>
+          <t>TBD_EST-039</t>
         </is>
       </c>
     </row>
@@ -47361,6 +50151,11 @@
           <t>EST-064</t>
         </is>
       </c>
+      <c r="W559" t="inlineStr">
+        <is>
+          <t>TBD_EST-064</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -47445,6 +50240,11 @@
           <t>EST-109</t>
         </is>
       </c>
+      <c r="W560" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -47527,6 +50327,11 @@
       <c r="V561" t="inlineStr">
         <is>
           <t>EST-079</t>
+        </is>
+      </c>
+      <c r="W561" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
         </is>
       </c>
     </row>
@@ -47611,6 +50416,11 @@
           <t>EST-096</t>
         </is>
       </c>
+      <c r="W562" t="inlineStr">
+        <is>
+          <t>TBD_EST-096</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -47695,6 +50505,11 @@
           <t>EST-110</t>
         </is>
       </c>
+      <c r="W563" t="inlineStr">
+        <is>
+          <t>TBD_EST-110</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -47779,6 +50594,11 @@
           <t>EST-046</t>
         </is>
       </c>
+      <c r="W564" t="inlineStr">
+        <is>
+          <t>TBD_EST-046</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -47861,6 +50681,11 @@
       <c r="V565" t="inlineStr">
         <is>
           <t>EST-043</t>
+        </is>
+      </c>
+      <c r="W565" t="inlineStr">
+        <is>
+          <t>TBD_EST-043</t>
         </is>
       </c>
     </row>
@@ -47945,6 +50770,11 @@
           <t>EST-007</t>
         </is>
       </c>
+      <c r="W566" t="inlineStr">
+        <is>
+          <t>TBD_EST-007</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -48029,6 +50859,11 @@
           <t>EST-003</t>
         </is>
       </c>
+      <c r="W567" t="inlineStr">
+        <is>
+          <t>TBD_EST-003</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -48111,6 +50946,11 @@
       <c r="V568" t="inlineStr">
         <is>
           <t>EST-037</t>
+        </is>
+      </c>
+      <c r="W568" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
         </is>
       </c>
     </row>
@@ -48195,6 +51035,11 @@
           <t>EST-063</t>
         </is>
       </c>
+      <c r="W569" t="inlineStr">
+        <is>
+          <t>TBD_EST-063</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -48279,6 +51124,11 @@
           <t>EST-076</t>
         </is>
       </c>
+      <c r="W570" t="inlineStr">
+        <is>
+          <t>TBD_EST-076</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -48363,6 +51213,11 @@
           <t>EST-006</t>
         </is>
       </c>
+      <c r="W571" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -48447,6 +51302,11 @@
           <t>EST-045</t>
         </is>
       </c>
+      <c r="W572" t="inlineStr">
+        <is>
+          <t>TBD_EST-045</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -48531,6 +51391,11 @@
           <t>EST-093</t>
         </is>
       </c>
+      <c r="W573" t="inlineStr">
+        <is>
+          <t>TBD_EST-093</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -48615,6 +51480,11 @@
           <t>EST-100</t>
         </is>
       </c>
+      <c r="W574" t="inlineStr">
+        <is>
+          <t>TBD_EST-100</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -48699,6 +51569,11 @@
           <t>EST-094</t>
         </is>
       </c>
+      <c r="W575" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -48783,6 +51658,11 @@
           <t>EST-074</t>
         </is>
       </c>
+      <c r="W576" t="inlineStr">
+        <is>
+          <t>TBD_EST-074</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -48867,6 +51747,11 @@
           <t>EST-001</t>
         </is>
       </c>
+      <c r="W577" t="inlineStr">
+        <is>
+          <t>TBD_EST-001</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -48949,6 +51834,11 @@
       <c r="V578" t="inlineStr">
         <is>
           <t>EST-079</t>
+        </is>
+      </c>
+      <c r="W578" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
         </is>
       </c>
     </row>
@@ -49033,6 +51923,11 @@
           <t>EST-101</t>
         </is>
       </c>
+      <c r="W579" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -49117,6 +52012,11 @@
           <t>EST-079</t>
         </is>
       </c>
+      <c r="W580" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -49201,6 +52101,11 @@
           <t>EST-077</t>
         </is>
       </c>
+      <c r="W581" t="inlineStr">
+        <is>
+          <t>TBD_EST-077</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -49285,6 +52190,11 @@
           <t>EST-107</t>
         </is>
       </c>
+      <c r="W582" t="inlineStr">
+        <is>
+          <t>TBD_EST-107</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -49369,6 +52279,11 @@
           <t>EST-033</t>
         </is>
       </c>
+      <c r="W583" t="inlineStr">
+        <is>
+          <t>TBD_EST-033</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -49451,6 +52366,11 @@
       <c r="V584" t="inlineStr">
         <is>
           <t>EST-001</t>
+        </is>
+      </c>
+      <c r="W584" t="inlineStr">
+        <is>
+          <t>TBD_EST-001</t>
         </is>
       </c>
     </row>
@@ -49535,6 +52455,11 @@
           <t>EST-037</t>
         </is>
       </c>
+      <c r="W585" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -49619,6 +52544,11 @@
           <t>EST-010</t>
         </is>
       </c>
+      <c r="W586" t="inlineStr">
+        <is>
+          <t>TBD_EST-010</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -49703,6 +52633,11 @@
           <t>EST-006</t>
         </is>
       </c>
+      <c r="W587" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -49787,6 +52722,11 @@
           <t>EST-031</t>
         </is>
       </c>
+      <c r="W588" t="inlineStr">
+        <is>
+          <t>TBD_EST-031</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -49871,6 +52811,11 @@
           <t>EST-055</t>
         </is>
       </c>
+      <c r="W589" t="inlineStr">
+        <is>
+          <t>TBD_EST-055</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -49955,6 +52900,11 @@
           <t>EST-050</t>
         </is>
       </c>
+      <c r="W590" t="inlineStr">
+        <is>
+          <t>TBD_EST-050</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -50039,6 +52989,11 @@
           <t>EST-060</t>
         </is>
       </c>
+      <c r="W591" t="inlineStr">
+        <is>
+          <t>TBD_EST-060</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -50123,6 +53078,11 @@
           <t>EST-101</t>
         </is>
       </c>
+      <c r="W592" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -50207,6 +53167,11 @@
           <t>EST-092</t>
         </is>
       </c>
+      <c r="W593" t="inlineStr">
+        <is>
+          <t>TBD_EST-092</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -50291,6 +53256,11 @@
           <t>EST-103</t>
         </is>
       </c>
+      <c r="W594" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -50375,6 +53345,11 @@
           <t>EST-054</t>
         </is>
       </c>
+      <c r="W595" t="inlineStr">
+        <is>
+          <t>TBD_EST-054</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -50459,6 +53434,11 @@
           <t>EST-048</t>
         </is>
       </c>
+      <c r="W596" t="inlineStr">
+        <is>
+          <t>TBD_EST-048</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -50543,6 +53523,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W597" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -50627,6 +53612,11 @@
           <t>EST-098</t>
         </is>
       </c>
+      <c r="W598" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -50711,6 +53701,11 @@
           <t>EST-061</t>
         </is>
       </c>
+      <c r="W599" t="inlineStr">
+        <is>
+          <t>TBD_EST-061</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -50795,6 +53790,11 @@
           <t>EST-085</t>
         </is>
       </c>
+      <c r="W600" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -50877,6 +53877,11 @@
       <c r="V601" t="inlineStr">
         <is>
           <t>EST-111</t>
+        </is>
+      </c>
+      <c r="W601" t="inlineStr">
+        <is>
+          <t>TBD_EST-111</t>
         </is>
       </c>
     </row>
@@ -50891,7 +53896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50933,6 +53938,34 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>Estate_Wise_DRC_Summary aggregates the synthetic DRC observations by estate. Use actual repeated estate measurements for real-world estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>estate_name (added 2026-10-17): temporary placeholders generated from the synthetic estate_id values (e.g. EST-001 -&gt; TBD_EST-001).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>These estate_name placeholders are NOT verified real-world estate names and must not be interpreted as identifying actual estates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>estate_id remains the stable identifier; verified real estate names may replace these placeholders in a future revision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>No other data, columns, or sheets were modified by this change.</t>
         </is>
       </c>
     </row>
@@ -50947,7 +53980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50986,6 +54019,11 @@
           <t>max_drc_pct</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>estate_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -51013,6 +54051,11 @@
       <c r="G2" t="n">
         <v>31.41912534559517</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TBD_EST-001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -51040,6 +54083,11 @@
       <c r="G3" t="n">
         <v>37.80425183938794</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TBD_EST-002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -51067,6 +54115,11 @@
       <c r="G4" t="n">
         <v>33.54637100667544</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TBD_EST-003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -51094,6 +54147,11 @@
       <c r="G5" t="n">
         <v>32.86287164091277</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TBD_EST-004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -51121,6 +54179,11 @@
       <c r="G6" t="n">
         <v>30.68185489493144</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TBD_EST-005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -51148,6 +54211,11 @@
       <c r="G7" t="n">
         <v>33.39701884082114</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TBD_EST-006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -51175,6 +54243,11 @@
       <c r="G8" t="n">
         <v>33.18681489474599</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TBD_EST-007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -51202,6 +54275,11 @@
       <c r="G9" t="n">
         <v>37.35079501039145</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TBD_EST-008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -51229,6 +54307,11 @@
       <c r="G10" t="n">
         <v>32.30340313482387</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TBD_EST-009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -51256,6 +54339,11 @@
       <c r="G11" t="n">
         <v>33.52771381614413</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TBD_EST-010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -51283,6 +54371,11 @@
       <c r="G12" t="n">
         <v>35.03687282096081</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TBD_EST-011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -51310,6 +54403,11 @@
       <c r="G13" t="n">
         <v>34.1365540327119</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TBD_EST-012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -51337,6 +54435,11 @@
       <c r="G14" t="n">
         <v>34.39638453368288</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TBD_EST-013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -51364,6 +54467,11 @@
       <c r="G15" t="n">
         <v>33.76561453660422</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TBD_EST-014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -51391,6 +54499,11 @@
       <c r="G16" t="n">
         <v>32.28375167857669</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TBD_EST-015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -51418,6 +54531,11 @@
       <c r="G17" t="n">
         <v>33.9102196566912</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TBD_EST-016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -51445,6 +54563,11 @@
       <c r="G18" t="n">
         <v>34.90165641083175</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TBD_EST-017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -51472,6 +54595,11 @@
       <c r="G19" t="n">
         <v>33.96678461010544</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TBD_EST-018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -51499,6 +54627,11 @@
       <c r="G20" t="n">
         <v>31.9936717186819</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TBD_EST-019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51526,6 +54659,11 @@
       <c r="G21" t="n">
         <v>32.47362568586344</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TBD_EST-020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51553,6 +54691,11 @@
       <c r="G22" t="n">
         <v>33.57783576711307</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TBD_EST-021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -51580,6 +54723,11 @@
       <c r="G23" t="n">
         <v>33.55940890267219</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TBD_EST-022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -51607,6 +54755,11 @@
       <c r="G24" t="n">
         <v>33.31771600750594</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TBD_EST-023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -51634,6 +54787,11 @@
       <c r="G25" t="n">
         <v>33.72239760375098</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TBD_EST-024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -51661,6 +54819,11 @@
       <c r="G26" t="n">
         <v>33.44313067341437</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TBD_EST-025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -51688,6 +54851,11 @@
       <c r="G27" t="n">
         <v>31.35692875140564</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TBD_EST-026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -51715,6 +54883,11 @@
       <c r="G28" t="n">
         <v>34.24428566632337</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TBD_EST-027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -51742,6 +54915,11 @@
       <c r="G29" t="n">
         <v>35.07717718444282</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TBD_EST-028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -51769,6 +54947,11 @@
       <c r="G30" t="n">
         <v>32.67607415849256</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TBD_EST-029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -51796,6 +54979,11 @@
       <c r="G31" t="n">
         <v>35.65615501454086</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TBD_EST-030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -51823,6 +55011,11 @@
       <c r="G32" t="n">
         <v>33.68628159604785</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>TBD_EST-031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -51850,6 +55043,11 @@
       <c r="G33" t="n">
         <v>33.81189236088437</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>TBD_EST-032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -51877,6 +55075,11 @@
       <c r="G34" t="n">
         <v>34.72230386904812</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>TBD_EST-033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -51904,6 +55107,11 @@
       <c r="G35" t="n">
         <v>34.84065663915855</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TBD_EST-034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -51931,6 +55139,11 @@
       <c r="G36" t="n">
         <v>33.86226893749566</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TBD_EST-035</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -51958,6 +55171,11 @@
       <c r="G37" t="n">
         <v>34.14916848843153</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TBD_EST-036</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -51985,6 +55203,11 @@
       <c r="G38" t="n">
         <v>33.26095763278704</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>TBD_EST-037</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -52012,6 +55235,11 @@
       <c r="G39" t="n">
         <v>34.7813036528085</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TBD_EST-038</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -52039,6 +55267,11 @@
       <c r="G40" t="n">
         <v>34.23014081244042</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TBD_EST-039</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -52066,6 +55299,11 @@
       <c r="G41" t="n">
         <v>32.30626723748274</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TBD_EST-040</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -52093,6 +55331,11 @@
       <c r="G42" t="n">
         <v>33.70191533810981</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TBD_EST-041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -52120,6 +55363,11 @@
       <c r="G43" t="n">
         <v>35.09954346050336</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>TBD_EST-042</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -52147,6 +55395,11 @@
       <c r="G44" t="n">
         <v>34.68194241769077</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TBD_EST-043</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -52174,6 +55427,11 @@
       <c r="G45" t="n">
         <v>31.07366527507045</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TBD_EST-044</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -52201,6 +55459,11 @@
       <c r="G46" t="n">
         <v>34.07320718064061</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TBD_EST-045</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -52228,6 +55491,11 @@
       <c r="G47" t="n">
         <v>32.551875084916</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TBD_EST-046</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -52255,6 +55523,11 @@
       <c r="G48" t="n">
         <v>33.53952392245143</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TBD_EST-047</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -52282,6 +55555,11 @@
       <c r="G49" t="n">
         <v>33.72834013588145</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TBD_EST-048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -52309,6 +55587,11 @@
       <c r="G50" t="n">
         <v>31.1227792802441</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TBD_EST-049</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -52336,6 +55619,11 @@
       <c r="G51" t="n">
         <v>34.16916650558686</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TBD_EST-050</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -52363,6 +55651,11 @@
       <c r="G52" t="n">
         <v>35.38610306951627</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TBD_EST-051</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -52390,6 +55683,11 @@
       <c r="G53" t="n">
         <v>32.11652074504223</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TBD_EST-052</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -52417,6 +55715,11 @@
       <c r="G54" t="n">
         <v>34.61592202466899</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TBD_EST-053</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -52444,6 +55747,11 @@
       <c r="G55" t="n">
         <v>36.25084386777759</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TBD_EST-054</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -52471,6 +55779,11 @@
       <c r="G56" t="n">
         <v>35.69438589623282</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>TBD_EST-055</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -52498,6 +55811,11 @@
       <c r="G57" t="n">
         <v>37.12191744572303</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TBD_EST-056</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -52525,6 +55843,11 @@
       <c r="G58" t="n">
         <v>31.88548929392617</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TBD_EST-057</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -52552,6 +55875,11 @@
       <c r="G59" t="n">
         <v>36.19838129842685</v>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TBD_EST-058</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -52579,6 +55907,11 @@
       <c r="G60" t="n">
         <v>31.55663491787332</v>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TBD_EST-059</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -52606,6 +55939,11 @@
       <c r="G61" t="n">
         <v>33.11320246041579</v>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TBD_EST-060</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -52633,6 +55971,11 @@
       <c r="G62" t="n">
         <v>33.50797383487102</v>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>TBD_EST-061</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -52660,6 +56003,11 @@
       <c r="G63" t="n">
         <v>32.73450015431812</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TBD_EST-062</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -52687,6 +56035,11 @@
       <c r="G64" t="n">
         <v>31.10682345193939</v>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TBD_EST-063</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -52714,6 +56067,11 @@
       <c r="G65" t="n">
         <v>32.94756725555169</v>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>TBD_EST-064</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -52741,6 +56099,11 @@
       <c r="G66" t="n">
         <v>35.80454694093586</v>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>TBD_EST-065</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -52768,6 +56131,11 @@
       <c r="G67" t="n">
         <v>33.38764708262806</v>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>TBD_EST-066</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -52795,6 +56163,11 @@
       <c r="G68" t="n">
         <v>34.71791567651235</v>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>TBD_EST-067</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -52822,6 +56195,11 @@
       <c r="G69" t="n">
         <v>33.15457612444867</v>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>TBD_EST-068</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -52849,6 +56227,11 @@
       <c r="G70" t="n">
         <v>30.63871702404148</v>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TBD_EST-069</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -52876,6 +56259,11 @@
       <c r="G71" t="n">
         <v>34.76886915023368</v>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>TBD_EST-070</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -52903,6 +56291,11 @@
       <c r="G72" t="n">
         <v>32.41895702815357</v>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>TBD_EST-071</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -52930,6 +56323,11 @@
       <c r="G73" t="n">
         <v>33.77287543293174</v>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>TBD_EST-072</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -52957,6 +56355,11 @@
       <c r="G74" t="n">
         <v>35.30139347353272</v>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>TBD_EST-073</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -52984,6 +56387,11 @@
       <c r="G75" t="n">
         <v>33.72419338173211</v>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>TBD_EST-074</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -53011,6 +56419,11 @@
       <c r="G76" t="n">
         <v>34.13907658846729</v>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>TBD_EST-075</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -53038,6 +56451,11 @@
       <c r="G77" t="n">
         <v>32.71007468312379</v>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TBD_EST-076</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -53065,6 +56483,11 @@
       <c r="G78" t="n">
         <v>32.93388962229626</v>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>TBD_EST-077</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -53092,6 +56515,11 @@
       <c r="G79" t="n">
         <v>34.43749136803267</v>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>TBD_EST-078</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -53119,6 +56547,11 @@
       <c r="G80" t="n">
         <v>35.0723368904706</v>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>TBD_EST-079</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -53146,6 +56579,11 @@
       <c r="G81" t="n">
         <v>33.83904762166796</v>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>TBD_EST-080</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -53173,6 +56611,11 @@
       <c r="G82" t="n">
         <v>33.05988827732688</v>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>TBD_EST-081</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -53200,6 +56643,11 @@
       <c r="G83" t="n">
         <v>33.96626382863031</v>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>TBD_EST-082</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -53227,6 +56675,11 @@
       <c r="G84" t="n">
         <v>34.62438043827103</v>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TBD_EST-083</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -53254,6 +56707,11 @@
       <c r="G85" t="n">
         <v>34.98304507783374</v>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TBD_EST-084</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -53281,6 +56739,11 @@
       <c r="G86" t="n">
         <v>34.28116841464396</v>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>TBD_EST-085</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -53308,6 +56771,11 @@
       <c r="G87" t="n">
         <v>35.10413520177957</v>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TBD_EST-086</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -53335,6 +56803,11 @@
       <c r="G88" t="n">
         <v>34.11073877019118</v>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>TBD_EST-087</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -53362,6 +56835,11 @@
       <c r="G89" t="n">
         <v>33.46400586032097</v>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>TBD_EST-088</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -53389,6 +56867,11 @@
       <c r="G90" t="n">
         <v>33.66266158830562</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>TBD_EST-089</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -53416,6 +56899,11 @@
       <c r="G91" t="n">
         <v>35.98576885941311</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>TBD_EST-090</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -53443,6 +56931,11 @@
       <c r="G92" t="n">
         <v>35.67740220639838</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>TBD_EST-091</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -53470,6 +56963,11 @@
       <c r="G93" t="n">
         <v>35.27816718764773</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>TBD_EST-092</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -53497,6 +56995,11 @@
       <c r="G94" t="n">
         <v>34.50021971909871</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>TBD_EST-093</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -53524,6 +57027,11 @@
       <c r="G95" t="n">
         <v>35.31484891438019</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TBD_EST-094</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -53551,6 +57059,11 @@
       <c r="G96" t="n">
         <v>32.75547643878955</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>TBD_EST-095</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -53578,6 +57091,11 @@
       <c r="G97" t="n">
         <v>35.07947220317668</v>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>TBD_EST-096</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -53605,6 +57123,11 @@
       <c r="G98" t="n">
         <v>34.16762457026852</v>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>TBD_EST-097</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -53632,6 +57155,11 @@
       <c r="G99" t="n">
         <v>35.95689534792803</v>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>TBD_EST-098</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -53659,6 +57187,11 @@
       <c r="G100" t="n">
         <v>30.95626965284499</v>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>TBD_EST-099</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -53686,6 +57219,11 @@
       <c r="G101" t="n">
         <v>34.56937829644126</v>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>TBD_EST-100</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -53713,6 +57251,11 @@
       <c r="G102" t="n">
         <v>33.88947781888771</v>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>TBD_EST-101</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -53740,6 +57283,11 @@
       <c r="G103" t="n">
         <v>31.1387410138079</v>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>TBD_EST-102</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -53767,6 +57315,11 @@
       <c r="G104" t="n">
         <v>35.69666673583717</v>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>TBD_EST-103</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -53794,6 +57347,11 @@
       <c r="G105" t="n">
         <v>33.75847488928574</v>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>TBD_EST-104</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -53821,6 +57379,11 @@
       <c r="G106" t="n">
         <v>32.51980464572333</v>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>TBD_EST-105</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -53848,6 +57411,11 @@
       <c r="G107" t="n">
         <v>34.74485407702647</v>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>TBD_EST-106</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -53875,6 +57443,11 @@
       <c r="G108" t="n">
         <v>34.4269039883373</v>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>TBD_EST-107</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -53902,6 +57475,11 @@
       <c r="G109" t="n">
         <v>32.53650289180289</v>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>TBD_EST-108</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -53929,6 +57507,11 @@
       <c r="G110" t="n">
         <v>36.9874502630206</v>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>TBD_EST-109</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -53956,6 +57539,11 @@
       <c r="G111" t="n">
         <v>34.25889552645503</v>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>TBD_EST-110</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -53983,6 +57571,11 @@
       <c r="G112" t="n">
         <v>32.14001223656327</v>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>TBD_EST-111</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -54010,6 +57603,11 @@
       <c r="G113" t="n">
         <v>32.15091035077232</v>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>TBD_EST-112</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -54037,6 +57635,11 @@
       <c r="G114" t="n">
         <v>33.74814749200284</v>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>TBD_EST-113</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -54064,6 +57667,11 @@
       <c r="G115" t="n">
         <v>31.83730413358469</v>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>TBD_EST-114</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -54091,6 +57699,11 @@
       <c r="G116" t="n">
         <v>34.68993295656966</v>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>TBD_EST-115</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -54118,6 +57731,11 @@
       <c r="G117" t="n">
         <v>34.52429615564277</v>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>TBD_EST-116</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -54145,6 +57763,11 @@
       <c r="G118" t="n">
         <v>32.26134822773892</v>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>TBD_EST-117</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -54172,6 +57795,11 @@
       <c r="G119" t="n">
         <v>33.92621292963413</v>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>TBD_EST-118</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -54199,6 +57827,11 @@
       <c r="G120" t="n">
         <v>34.03933293229257</v>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>TBD_EST-119</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -54225,6 +57858,11 @@
       </c>
       <c r="G121" t="n">
         <v>31.2192571156079</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>TBD_EST-120</t>
+        </is>
       </c>
     </row>
   </sheetData>
